--- a/public/business-plans/industry.xlsx
+++ b/public/business-plans/industry.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,10 @@
       <sz val="13"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
     <font>
@@ -66,12 +70,17 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -115,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,19 +133,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -558,10 +570,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Промышленность». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
+          <t>Это готовый образец (шаблон) бизнес-плана MoliyaHub для отрасли «Промышленность». Замените текст в квадратных скобках [впишите] и примеры на данные вашего проекта, добавьте или удалите строки в таблицах по необходимости. Абзацы, отмеченные как «ПРИМЕР», — иллюстрация формата ответа, а не факты о реальной компании; замените их своими данными. Суммы в листе «Финансовый план» пересчитываются автоматически по формулам — просто впишите свои цифры в столбец «Сумма, сум».</t>
         </is>
       </c>
     </row>
@@ -579,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -592,125 +604,45 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="89" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): ООО «Vodiy Tekstil» открывает швейный цех полного цикла в Ферганской области на 40 рабочих мест: закупка хлопковой пряжи у местного кластера, пошив трикотажных изделий для экспорта в Казахстан и Россию. Требуемые инвестиции — 850 млн сум на оборудование и оборотный капитал на первую партию; срок окупаемости — около 18 месяцев за счёт контракта с оптовым дистрибьютором на первый год.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] В 5-8 предложениях: суть проекта, какую проблему решает, для кого, требуемая сумма инвестиций и на что она пойдёт, ожидаемый результат (выручка/прибыль/срок окупаемости).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Описание компании / проекта</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Организационно-правовая форма (ИП/ООО/фермерское хозяйство), команда, текущий статус проекта (идея / MVP / действующий бизнес), уникальное торговое предложение.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:D5"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Анализ рынка: Промышленность</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>•  Узбекистан — один из крупнейших мировых производителей хлопка-волокна; сырьевая база для текстильной и швейной отрасли — на месте.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>•  Текстильная и швейная промышленность — приоритетный экспортный сектор: действуют кластерная система, свободные экономические зоны и налоговые льготы для производителей.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>•  Растёт экспорт в страны СНГ и ЕС (в т.ч. по преференциальным режимам) — учитывайте требования к качеству и сертификации на целевом рынке.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>•  [Впишите] Объём и динамику конкретного продуктового сегмента, ключевых конкурентов и их долю рынка — эти данные лучше собрать под конкретный продукт (отраслевая статистика Госкомстата, отраслевые ассоциации).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Конкуренты</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Список из 3-5 прямых конкурентов, их сильные и слабые стороны, чем вы отличаетесь.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Целевая аудитория</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Портрет основного клиента: кто он, что для него важно при выборе, где его найти.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -725,121 +657,307 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
+          <t>Анализ рынка: Промышленность</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="59" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>•  Узбекистан — один из крупнейших мировых производителей хлопка-волокна; сырьевая база для текстильной и швейной отрасли — на месте, что снижает валютные риски по сырью по сравнению с странами-импортёрами хлопка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="59" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>•  Текстильная и швейная промышленность — приоритетный экспортный сектор: действуют кластерная система (от хлопка до готового изделия в одной цепочке), свободные экономические зоны и налоговые льготы для производителей-экспортёров.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="74" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>•  По данным Госкомстата, за январь–апрель 2026 года Узбекистан экспортировал текстильной продукции на $454,5 млн (готовые изделия — 50%, пряжа — 32%), что заметно ниже уровня аналогичного периода 2025 года (около $840 млн) — отрасль ощущает давление внешнего спроса и ценовой конкуренции, планировать выручку на экспорт стоит консервативно (stat.uz).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="74" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>•  Для сравнения: Турция и Пакистан остаются крупнейшими конкурентами на глобальном рынке текстиля и швейных изделий за счёт масштаба производства и близости к морским портам; Узбекистан конкурирует прежде всего собственным хлопковым сырьём и льготными условиями в кластерах — логистика в ЕС/США у него дороже и дольше.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="59" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>•  Растёт экспорт в страны СНГ и ЕС (Узбекистан имеет преференциальный режим GSP+ с ЕС на часть товарных позиций) — учитывайте требования к качеству, сертификации (ISO, Oeko-Tex для текстиля) и происхождению товара на целевом рынке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="74" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>•  Горнодобыча и металлургия (золото, медь, урановое сырьё) — капиталоёмкие подотрасли с доминированием крупных государственных холдингов (АГМК, НГМК); малому и среднему бизнесу здесь реалистичнее заходить через сервис и подряд (обслуживание техники, транспорт, стройка на объектах), а не через добычу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="59" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>•  Химическая, фармацевтическая и стройматериальная подотрасли растут за счёт импортозамещения и госпрограмм локализации — субсидии и таможенные льготы на оборудование для локализуемых производств стоит проверять по актуальному перечню Мининвестпрома на момент запуска.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="59" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>•  [Впишите] Объём и динамику конкретного продуктового сегмента, ключевых конкурентов и их долю рынка — эти данные лучше собрать под конкретный продукт (отраслевая статистика Госкомстата, отраслевые ассоциации, таможенная статистика).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Конкуренты</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[Впишите] Список из 3-5 прямых конкурентов, их сильные и слабые стороны, чем вы отличаетесь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Целевая аудитория</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>[Впишите] Портрет основного клиента: кто он, что для него важно при выборе, где его найти.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
           <t>Маркетинговый план</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="74" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цена — на 10-15% ниже турецких аналогов за счёт местного сырья; продажи через прямые контракты с 3 оптовыми сетями в Казахстане и участие в отраслевых выставках (Uzbekistan Textile Expo); первые заказы — через существующие связи владельца в отрасли и каталог на B2B-платформах.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Ценообразование, каналы продвижения и продаж, план привлечения первых клиентов.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Операционный план</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5" ht="74" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Цикл: приём пряжи от кластера → вязка полотна → раскрой → пошив → упаковка → отгрузка. Ключевой поставщик сырья — местный хлопково-текстильный кластер по долгосрочному договору. Необходимые разрешения: сертификат соответствия на продукцию, при экспорте — сертификат происхождения товара.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>[Впишите] Процесс производства/оказания услуги, ключевые поставщики, оборудование, необходимые лицензии и разрешения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Организационный план</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>Организационный план</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="59" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ПРИМЕР (иллюстрация, не данные реальной компании): Директор-учредитель, технолог производства, 2 мастера смены, 36 швей, бухгалтер на аутсорсе. Форма — ООО (общество с ограниченной ответственностью), упрощённый налоговый режим на старте.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[Впишите] Команда и роли, штатное расписание, организационно-правовая форма.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>Риски и меры по их снижению (примеры для отрасли)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Риск</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Меры снижения</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Колебания курса при импорте сырья/оборудования</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Фиксировать цены в договорах, диверсифицировать поставщиков</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Дефицит квалифицированных кадров</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Обучение на месте, партнёрство с колледжами/техникумами</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Изменение экспортных пошлин/квот</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Мониторинг госпрограмм поддержки экспорта (Uzexport и др.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="13" ht="59" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Колебания курса при импорте оборудования и части фурнитуры</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Фиксировать цены в договорах, закупать оборудование партиями, диверсифицировать поставщиков</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Дефицит квалифицированных кадров (технологи, наладчики оборудования)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Обучение на месте, партнёрство с колледжами/техникумами, стажировки</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="59" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Изменение экспортных пошлин, квот или условий преференциальных режимов (GSP+)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Мониторинг госпрограмм поддержки экспорта (Uzexport, торговые представительства), консультации с таможенными брокерами</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Падение экспортных цен/спроса на внешних рынках (как в начале 2026 года)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Диверсификация рынков сбыта, часть продукции — на внутренний рынок и в страны СНГ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Рост цен на энергоносители и перебои электроснабжения на производстве</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Энергоаудит, резервное электропитание для критичных узлов, энергоэффективное оборудование</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Задержки поставок сырья от кластера/поставщиков в пиковый сезон</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Страховой запас сырья на 1-2 месяца, альтернативные поставщики</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>[Впишите] Дополните таблицу своими рисками, специфичными для вашего проекта и региона.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="21">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -851,382 +969,423 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Статья</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Сумма, сум</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Добавляйте свои строки при необходимости.</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n"/>
-      <c r="C6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Аренда/ремонт производственного помещения</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>разовый ремонт + депозит</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Оборудование (станки, линии)</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Оборудование (станки, швейные/вязальные линии)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>новое или б/у</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Сырьё на первую партию</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="B9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>запас на 1-2 месяца</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Регистрация юрлица и разрешения</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="B10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>включая сертификацию продукции</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Спецодежда и охрана труда</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="B11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Пусконаладка и обучение персонала работе на оборудовании</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Оборотный капитал на первые 1-2 месяца</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="B13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>зарплата и текущие расходы до первых продаж</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Итого: стартовые затраты (единоразово)</t>
         </is>
       </c>
-      <c r="B13" s="15">
-        <f>SUM(B7:B12)</f>
+      <c r="B14" s="16">
+        <f>SUM(B7:B13)</f>
         <v/>
       </c>
-      <c r="C13" s="16" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="C14" s="17" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Оптовые продажи</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="B17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>торговым сетям/дистрибьюторам</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Розничные продажи / маркетплейсы</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="B18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Экспортные поставки</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="B19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>по прямым контрактам</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Услуги давальческой переработки (толлинг)</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>пошив/обработка из сырья заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячная выручка</t>
         </is>
       </c>
-      <c r="B19" s="15">
-        <f>SUM(B16:B18)</f>
+      <c r="B21" s="16">
+        <f>SUM(B17:B20)</f>
         <v/>
       </c>
-      <c r="C19" s="16" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="C21" s="17" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Аренда помещения</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="B24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>ФОТ производственного персонала</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="B25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>включая соцотчисления</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Сырьё и материалы</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="B26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Электроэнергия и коммунальные услуги</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="B27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Логистика и упаковка</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="B28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Сертификация и лабораторные испытания продукции</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>периодические затраты, не только при запуске</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Налоги</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="B30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>ЕНП/НДС по применимому режиму</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Маркетинг и продвижение</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="13" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="B31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Итого: ежемесячные операционные расходы</t>
         </is>
       </c>
-      <c r="B29" s="15">
-        <f>SUM(B22:B28)</f>
+      <c r="B32" s="16">
+        <f>SUM(B24:B31)</f>
         <v/>
       </c>
-      <c r="C29" s="16" t="n"/>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="C32" s="17" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Ежемесячная прибыль</t>
         </is>
       </c>
-      <c r="B31" s="10">
-        <f>B19-B29</f>
+      <c r="B34" s="11">
+        <f>B21-B32</f>
         <v/>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Срок выхода на окупаемость, мес.</t>
         </is>
       </c>
-      <c r="B33" s="13">
-        <f>IFERROR(B4/B31,"—")</f>
+      <c r="B36" s="14">
+        <f>IFERROR(B4/B34,"—")</f>
         <v/>
       </c>
-      <c r="C33" s="13">
+      <c r="C36" s="14">
         <f> Начальные инвестиции / Ежемесячная прибыль</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Рентабельность продаж, %</t>
         </is>
       </c>
-      <c r="B34" s="17">
-        <f>IFERROR(B31/B19*100,"—")</f>
+      <c r="B37" s="18">
+        <f>IFERROR(B34/B21*100,"—")</f>
         <v/>
       </c>
-      <c r="C34" s="13">
+      <c r="C37" s="14">
         <f> Ежемесячная прибыль / Выручка × 100%</f>
         <v/>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта.</t>
+    <row r="38"/>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A36:C36"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A39:C39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/business-plans/industry.xlsx
+++ b/public/business-plans/industry.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001D4ED8"/>
     </font>
   </fonts>
   <fills count="5">
@@ -103,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,6 +126,9 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -498,14 +505,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ФИНАНСОВЫЙ ПЛАН: ПРОМЫШЛЕННОСТЬ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="45" customHeight="1">
+          <t>ФИНАНСОВЫЙ ПЛАН: ПРОМЫШЛЕННОСТЬ — ПРИМЕР РАСЧЁТА</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Промышленность» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — только расчётная часть с рабочими формулами.</t>
+          <t>Этот файл дополняет текстовый документ бизнес-плана MoliyaHub для отрасли «Промышленность» (резюме, анализ рынка, маркетинговый/операционный/организационный план, риски — в Word-файле с тем же названием). Здесь — расчётная часть с рабочими формулами, уже заполненная цифрами ПРИМЕРА (иллюстративная компания из резюме бизнес-плана, не реальный заёмщик) — чтобы показать порядок величины и логику расчёта. Перед подачей в банк или инвестору замените суммы на данные своего проекта.</t>
         </is>
       </c>
     </row>
@@ -527,10 +534,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Впишите свои суммы в столбец «Сумма, сум» напротив каждой строки — итоги и срок окупаемости ниже пересчитаются автоматически (это формулы, не готовые числа). Строки без сумм — примерные статьи для вашей отрасли, добавляйте свои при необходимости.</t>
+          <t>Столбец «Сумма, сум» уже заполнен примером расчёта для иллюстративной компании из этого бизнес-плана — на основе рыночных ориентиров 2025-2026 года (там, где источник известен — со ссылкой в комментарии) или экспертной оценки порядка величины (это тоже отмечено). Итоги, прибыль, срок окупаемости и рентабельность ниже пересчитаются автоматически (это формулы). Замените суммы в столбце B на данные вашего собственного проекта — тогда пересчитается всё.</t>
         </is>
       </c>
     </row>
@@ -541,8 +548,9 @@
           <t>Начальные инвестиции (требуемая сумма)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>0</v>
+      <c r="B7" s="6">
+        <f>B17</f>
+        <v/>
       </c>
     </row>
     <row r="8"/>
@@ -555,100 +563,108 @@
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="8" t="n"/>
     </row>
-    <row r="10" ht="21" customHeight="1">
+    <row r="10" ht="66" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Аренда/ремонт производственного помещения</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0</v>
+        <v>130000000</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>разовый ремонт + депозит</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
+          <t>разовый ремонт + депозит — Пример: оценка: ремонт цеха ~800-1000 м² в Ферганской обл. + депозит; пром. аренда в регионах в 2-3 раза ниже ташкентской (офисы Ташкента ~$26/м²/мес, CMWP/spot.uz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="51" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Оборудование (станки, швейные/вязальные линии)</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0</v>
+        <v>400000000</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>новое или б/у</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="21" customHeight="1">
+          <t>новое или б/у — Пример: оценка: ~45 промышленных швейных машин (~6 млн сум/шт с доставкой) + 2-3 кругловязальные машины + раскройное/утюжильное оборудование</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Сырьё на первую партию</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0</v>
+        <v>160000000</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>запас на 1-2 месяца</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="21" customHeight="1">
+          <t>запас на 1-2 месяца — Пример: оценка: запас пряжи на ~1 мес. производства при доле сырья ~42% в себестоимости</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Регистрация юрлица и разрешения</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>включая сертификацию продукции</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
+          <t>включая сертификацию продукции — Пример: оценка: госпошлины за регистрацию ООО, разрешения СЭС и пожарного надзора</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Спецодежда и охрана труда</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="inlineStr"/>
-    </row>
-    <row r="15" ht="21" customHeight="1">
+        <v>17000000</v>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: комплекты на 40+ работников (~300 тыс. сум/компл.) + средства охраны труда</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Пусконаладка и обучение персонала работе на оборудовании</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr"/>
-    </row>
-    <row r="16" ht="21" customHeight="1">
+        <v>15000000</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: шеф-монтаж линий поставщиком и обучение персонала</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="51" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Оборотный капитал на первые 1-2 месяца</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>зарплата и текущие расходы до первых продаж</t>
+          <t>зарплата и текущие расходы до первых продаж — Пример: оценка: ФОТ, аренда и текущие расходы до первых оплат от покупателей</t>
         </is>
       </c>
     </row>
@@ -674,59 +690,63 @@
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="8" t="n"/>
     </row>
-    <row r="20" ht="21" customHeight="1">
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Оптовые продажи</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>0</v>
+        <v>171500000</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>торговым сетям/дистрибьюторам</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="21" customHeight="1">
+          <t>торговым сетям/дистрибьюторам — Пример: 35% от выручки — оценка структуры сбыта на внутреннем рынке</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Розничные продажи / маркетплейсы</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9" t="inlineStr"/>
-    </row>
-    <row r="22" ht="21" customHeight="1">
+        <v>49000000</v>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Пример: 10% от выручки — оценка доли прямых продаж (Uzum Market и аналоги)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Экспортные поставки</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0</v>
+        <v>220500000</v>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>по прямым контрактам</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="21" customHeight="1">
+          <t>по прямым контрактам — Пример: 45% от выручки — экспорт в Казахстан и Россию облагается НДС по ставке 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="51" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Услуги давальческой переработки (толлинг)</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0</v>
+        <v>49000000</v>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>пошив/обработка из сырья заказчика</t>
+          <t>пошив/обработка из сырья заказчика — Пример: 10% от выручки — толлинговые заказы, распространённая практика в текстильном кластере Ферганской обл.</t>
         </is>
       </c>
     </row>
@@ -752,105 +772,125 @@
       <c r="B26" s="8" t="n"/>
       <c r="C26" s="8" t="n"/>
     </row>
-    <row r="27" ht="21" customHeight="1">
+    <row r="27" ht="36" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Аренда помещения</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28" ht="21" customHeight="1">
+        <v>16000000</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: ~800 м² по ~20 тыс. сум/м²/мес — ориентир для промышленной недвижимости в регионе</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="66" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>ФОТ производственного персонала</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>0</v>
+        <v>156500000</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>включая соцотчисления</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="21" customHeight="1">
+          <t>включая соцотчисления — Пример: 40 швей + технолог + 2 мастера + директор + бухгалтер на аутсорсе; ориентир — средняя зарплата по Ферганской обл. ~4,73 млн сум/мес (Госкомстат/gazeta.uz), сдельная ставка швеи обычно ниже</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Сырьё и материалы</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30" ht="21" customHeight="1">
+        <v>205800000</v>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Пример: ~42% от выручки — типовая доля материальных затрат в себестоимости трикотажного производства</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Электроэнергия и коммунальные услуги</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31" ht="21" customHeight="1">
+        <v>15000000</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка для цеха с ~40 швейными машинами и вязальными линиями</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Логистика и упаковка</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32" ht="21" customHeight="1">
+        <v>14700000</v>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Пример: ~3% от выручки — упаковка и транспортировка, включая экспорт в РФ/КЗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="51" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Сертификация и лабораторные испытания продукции</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>периодические затраты, не только при запуске</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="21" customHeight="1">
+          <t>периодические затраты, не только при запуске — Пример: оценка: усреднённые ежемесячные расходы на сертификаты соответствия</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="51" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Налоги</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>0</v>
+        <v>28000000</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>ЕНП/НДС по применимому режиму</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="21" customHeight="1">
+          <t>ЕНП/НДС по применимому режиму — Пример: соц. налог 12% от ФОТ (2026 г.) + оценка налога на прибыль 15% + имущественный/земельный налог</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Маркетинг и продвижение</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="9" t="inlineStr"/>
+        <v>5000000</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Пример: оценка: продвижение на маркетплейсах и поиск оптовых/экспортных партнёров</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -887,9 +927,10 @@
         <f>IFERROR(B7/B37,"—")</f>
         <v/>
       </c>
-      <c r="C39" s="9">
-        <f> Начальные инвестиции / Ежемесячная прибыль</f>
-        <v/>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Начальные инвестиции ÷ Ежемесячная прибыль</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -902,24 +943,34 @@
         <f>IFERROR(B37/B24*100,"—")</f>
         <v/>
       </c>
-      <c r="C40" s="9">
-        <f> Ежемесячная прибыль / Выручка × 100%</f>
-        <v/>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Формула: Ежемесячная прибыль ÷ Выручка × 100%</t>
+        </is>
       </c>
     </row>
     <row r="41"/>
-    <row r="42" ht="40" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Это шаблон для ваших собственных расчётов, а не готовые рыночные данные — цифры нужно заполнить самостоятельно, исходя из реальных цен и условий вашего проекта. Там, где в комментарии указан ориентир или диапазон, — это иллюстрация для понимания масштаба статьи, а не проверенные рыночные данные.</t>
+    <row r="42" ht="50" customHeight="1">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Как считался этот пример: Расчётная сумма стартовых затрат — 847 млн сум, практически совпадает с заявленными 850 млн. Расчётная прибыль ≈46 млн сум/мес даёт окупаемость ≈18,5 мес. — соответствует резюме.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="55" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Это пример расчёта для иллюстративной компании, а не готовая заявка на кредит и не проверенные рыночные данные о реальном бизнесе. Суммы в столбце B — рабочие формулы: замените их на цифры вашего проекта, и итоги, прибыль, срок окупаемости и рентабельность пересчитаются автоматически. Там, где в комментарии указан источник — это ориентир на 2025-2026 год, проверяйте актуальность перед подачей документов в банк; где указана «экспертная оценка» — это иллюстрация порядка величины, а не факт.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A44:C44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
